--- a/textbook_examples/mod01_conditional_practice.xlsx
+++ b/textbook_examples/mod01_conditional_practice.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Conditional" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,35 +28,41 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
+      <color rgb="FF4A7C59"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="005C6B62"/>
+      <family val="2"/>
+      <color rgb="FF5C6B62"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0024302A"/>
+      <family val="2"/>
+      <color rgb="FF24302A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="002F5D46"/>
+      <family val="2"/>
+      <color rgb="FF2F5D46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="0024302A"/>
+      <color rgb="FF24302A"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -70,7 +75,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="FF4A7C59"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,12 +91,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -110,10 +112,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -477,280 +484,280 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" style="11" min="1" max="1"/>
+    <col width="15" customWidth="1" style="11" min="2" max="2"/>
+    <col width="11" customWidth="1" style="11" min="3" max="3"/>
+    <col width="13" customWidth="1" style="11" min="4" max="4"/>
+    <col width="11" customWidth="1" style="11" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="11">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Conditional functions</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="44" customHeight="1" s="11">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Eight fields, each with a crop and a yield.  The functions below all answer questions about a SUBSET of the rows — only the canola fields, only the yields above a threshold.  Column F shows the formula that produced column E.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="11"/>
+    <row r="4" ht="18" customHeight="1" s="11">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Crop</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Acres</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Yield (bu/ac)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Above 50?</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="11">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Canola</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="7" t="n">
         <v>41.2</v>
       </c>
-      <c r="E5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="11">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>South</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Wheat</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7" t="n">
         <v>58.6</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="11">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Creek</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Canola</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>37.9</v>
       </c>
-      <c r="E7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="11">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Barley</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="E8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="11">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Rented</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wheat</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>61.3</v>
       </c>
-      <c r="E9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="11">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Airport</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Canola</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="7" t="n">
         <v>44.8</v>
       </c>
-      <c r="E10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Hill</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Barley</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>275</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="7" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="E11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="11">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Slough</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Wheat</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>330</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="7" t="n">
         <v>55.2</v>
       </c>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="E12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="11"/>
+    <row r="14" ht="18" customHeight="1" s="11">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Questions about a subset</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="11">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>How many canola fields?</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="11">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Total canola acres</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="11">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Average canola yield</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="11">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>How many yields above 60?</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="11">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Average wheat yield over 250 ac</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="11">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>How many above the average?</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1"/>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="11"/>
+    <row r="22" ht="32" customHeight="1" s="11">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>The last one is the awkward case: the threshold is itself a calculation, so you glue "&gt;" onto it with &amp;.  Quoting the whole thing as "&gt;AVERAGE(...)" would search for that literal text.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1"/>
+    <row r="23" ht="18" customHeight="1" s="11"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
